--- a/out/LSTM-Mamba1_repeat_3_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.073179781458245</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.073179781458245</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.473179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.473179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.473179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_3_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.5979430258540229</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.5979430258540229</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.3979430258540229</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.3979430258540229</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.473179781458245</v>
+        <v>-0.3979430258540229</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.473179781458245</v>
+        <v>-1.055894707285653</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.055894707285653</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.3979430258540229</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.473179781458245</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.5979430258540229</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.073179781458245</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.073179781458245</v>
+        <v>-0.5979430258540231</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.06000865557760773</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.9179603370092387</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092387</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.06000865557760773</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.073179781458245</v>
+        <v>0.06000865557760772</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.2689671851382078</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_3_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02272793278098106</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.0126569289714098</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.006944958120584488</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.00379398837685585</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001750074326992035</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.000619448721408844</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-9.000301361083984e-05</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5979430258540229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0006714537739753723</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001721154898405075</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001444358378648758</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0007940717041492462</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0003219880163669586</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0004638545215129852</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0005459785461425781</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0006133280694484711</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9179603370092387</v>
+        <v>-0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0007317699491977692</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9179603370092387</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.000898405909538269</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001003533601760864</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001005683094263077</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001104503870010376</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001214288175106049</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001188468188047409</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001183543354272842</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002369191497564316</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002341758459806442</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001914490014314651</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001609973609447479</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001353546977043152</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001036379486322403</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0008501894772052765</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0009059198200702667</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0009554661810398102</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001083735376596451</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001273222267627716</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001658074557781219</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002388380467891693</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.002382710576057434</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001930259168148041</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002184517681598663</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002522889524698257</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003038320690393448</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.003696966916322708</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002987220883369446</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.003813114017248154</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0009012185037136078</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001589689403772354</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5979430258540229</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003277700394392014</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003461986780166626</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.003537092357873917</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002006281167268753</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001660339534282684</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001891795545816422</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002532437443733215</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002942834049463272</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002592667937278748</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002486869692802429</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002154480665922165</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001383166760206223</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001039896160364151</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0009746663272380829</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0005341805517673492</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.000713735818862915</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001167945563793182</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.0009637661278247833</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0004102922976016998</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3979430258540229</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0002257786691188812</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3979430258540229</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0002368055284023285</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3979430258540229</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001338768750429153</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.055894707285653</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002088055014610291</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.055894707285653</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.002352211624383926</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002180814743041992</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002091512084007263</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.001695260405540466</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.001425109803676605</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001347295939922333</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00114532932639122</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0008109323680400848</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0006000734865665436</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.0004564113914966583</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0002633519470691681</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.255894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-5.992501974105835e-05</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3979430258540229</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0002337321639060974</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0002422593533992767</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0002353750169277191</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0001387596130371094</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-4.351511597633362e-05</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0001195706427097321</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0002846680581569672</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.0007876977324485779</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0004193410277366638</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>4.898384213447571e-05</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>3.974884748458862e-06</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2600086555776079</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0002566128969192505</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5979430258540229</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0004590079188346863</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0004889145493507385</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-5.23589551448822e-05</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5979430258540231</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>4.484131932258606e-05</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.06000865557760773</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>9.278953075408936e-05</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0001055151224136353</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0003549493849277496</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0002830438315868378</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0004011094570159912</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0005967728793621063</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0006173774600028992</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0006843730807304382</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0007216557860374451</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0006864182651042938</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0006997138261795044</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0008142478764057159</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0008651763200759888</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.001108840107917786</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.001134958118200302</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001258499920368195</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.001240365207195282</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001315202564001083</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.002143748104572296</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.00234491378068924</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.003407243639230728</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.00258912518620491</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7179603370092387</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.002218306064605713</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.001117009669542313</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0002865791320800781</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7179603370092387</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0001016296446323395</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.06000865557760773</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0001052431762218475</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.06000865557760772</v>
+        <v>-1</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0005270279943943024</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2689671851382078</v>
+        <v>-1.14</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_3_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.02272793278098106</v>
+        <v>-0.02272796630859375</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.0126569289714098</v>
+        <v>-0.01265698298811913</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.006944958120584488</v>
+        <v>-0.00694497674703598</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.00379398837685585</v>
+        <v>-0.003793969750404358</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001750074326992035</v>
+        <v>-0.001750100404024124</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.000619448721408844</v>
+        <v>-0.0006194561719894409</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-9.000301361083984e-05</v>
+        <v>-9.006261825561523e-05</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.0006714537739753723</v>
+        <v>0.0006714202463626862</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.02000000000000007</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.001721154898405075</v>
+        <v>0.001721084117889404</v>
       </c>
       <c r="JB10" t="n">
         <v>0.8599999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.001444358378648758</v>
+        <v>0.001444313675165176</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.0007940717041492462</v>
+        <v>0.0007939822971820831</v>
       </c>
       <c r="JB12" t="n">
         <v>0.8599999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0003219880163669586</v>
+        <v>0.0003218688070774078</v>
       </c>
       <c r="JB13" t="n">
         <v>0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0004638545215129852</v>
+        <v>0.0004638060927391052</v>
       </c>
       <c r="JB14" t="n">
         <v>0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0005459785461425781</v>
+        <v>0.000545889139175415</v>
       </c>
       <c r="JB15" t="n">
         <v>0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0006133280694484711</v>
+        <v>0.000613238662481308</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0007317699491977692</v>
+        <v>0.0007316656410694122</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.000898405909538269</v>
+        <v>0.000898316502571106</v>
       </c>
       <c r="JB18" t="n">
         <v>0.1199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.001003533601760864</v>
+        <v>0.001003522425889969</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001005683094263077</v>
+        <v>0.001005642116069794</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.001104503870010376</v>
+        <v>0.001104440540075302</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001214288175106049</v>
+        <v>0.001214276999235153</v>
       </c>
       <c r="JB22" t="n">
         <v>0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001188468188047409</v>
+        <v>0.001188494265079498</v>
       </c>
       <c r="JB23" t="n">
         <v>0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.001183543354272842</v>
+        <v>0.001183554530143738</v>
       </c>
       <c r="JB24" t="n">
         <v>0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.002369191497564316</v>
+        <v>0.002369172871112823</v>
       </c>
       <c r="JB25" t="n">
         <v>0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.002341758459806442</v>
+        <v>0.002341728657484055</v>
       </c>
       <c r="JB26" t="n">
         <v>0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.001914490014314651</v>
+        <v>0.001914449036121368</v>
       </c>
       <c r="JB27" t="n">
         <v>0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001609973609447479</v>
+        <v>0.00160994753241539</v>
       </c>
       <c r="JB28" t="n">
         <v>0.2599999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.001353546977043152</v>
+        <v>0.001353505998849869</v>
       </c>
       <c r="JB29" t="n">
         <v>0.1199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001036379486322403</v>
+        <v>0.001036357134580612</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.02000000000000007</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0008501894772052765</v>
+        <v>0.0008501447737216949</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0009059198200702667</v>
+        <v>0.0009058937430381775</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0009554661810398102</v>
+        <v>0.0009554065763950348</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.16</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001083735376596451</v>
+        <v>0.001083660870790482</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001273222267627716</v>
+        <v>0.001273248344659805</v>
       </c>
       <c r="JB35" t="n">
         <v>0.1199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.001658074557781219</v>
+        <v>0.001658055931329727</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.002388380467891693</v>
+        <v>0.002388350665569305</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.002382710576057434</v>
+        <v>0.002382662147283554</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001930259168148041</v>
+        <v>0.001930225640535355</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.002184517681598663</v>
+        <v>0.002184454351663589</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.002522889524698257</v>
+        <v>0.002522833645343781</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.003038320690393448</v>
+        <v>0.003038201481103897</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.003696966916322708</v>
+        <v>0.003696631640195847</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002987220883369446</v>
+        <v>0.002987198531627655</v>
       </c>
       <c r="JB44" t="n">
         <v>0.1199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.003813114017248154</v>
+        <v>0.003812924027442932</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0009012185037136078</v>
+        <v>0.0009009763598442078</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001589689403772354</v>
+        <v>-0.001589905470609665</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.003277700394392014</v>
+        <v>-0.003277778625488281</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.003461986780166626</v>
+        <v>-0.003461908549070358</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.003537092357873917</v>
+        <v>-0.003537077456712723</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.002006281167268753</v>
+        <v>-0.00200628861784935</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.001660339534282684</v>
+        <v>-0.001660507172346115</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.002532437443733215</v>
+        <v>-0.002532422542572021</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002942834049463272</v>
+        <v>-0.002942867577075958</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002592667937278748</v>
+        <v>-0.002592694014310837</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002486869692802429</v>
+        <v>-0.002486992627382278</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.002154480665922165</v>
+        <v>-0.002154570072889328</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.001383166760206223</v>
+        <v>-0.00138324499130249</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.001039896160364151</v>
+        <v>-0.001039993017911911</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0009746663272380829</v>
+        <v>-0.000974748283624649</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.0005341805517673492</v>
+        <v>-0.00053420290350914</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.000713735818862915</v>
+        <v>-0.0007138252258300781</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001167945563793182</v>
+        <v>-0.00116797536611557</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.2599999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.0009637661278247833</v>
+        <v>-0.0009638033807277679</v>
       </c>
       <c r="JB65" t="n">
         <v>0.02000000000000007</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0004102922976016998</v>
+        <v>-0.0004103705286979675</v>
       </c>
       <c r="JB66" t="n">
         <v>0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.0002257786691188812</v>
+        <v>0.000225502997636795</v>
       </c>
       <c r="JB67" t="n">
         <v>0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0002368055284023285</v>
+        <v>-0.0002368837594985962</v>
       </c>
       <c r="JB68" t="n">
         <v>0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.001338768750429153</v>
+        <v>-0.001338746398687363</v>
       </c>
       <c r="JB69" t="n">
         <v>0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002088055014610291</v>
+        <v>-0.002088058739900589</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.1199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.002352211624383926</v>
+        <v>-0.002352267503738403</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002180814743041992</v>
+        <v>-0.002180863171815872</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.002091512084007263</v>
+        <v>-0.002091530710458755</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.001695260405540466</v>
+        <v>-0.001695301383733749</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.001425109803676605</v>
+        <v>-0.001425176858901978</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001347295939922333</v>
+        <v>-0.001347336918115616</v>
       </c>
       <c r="JB76" t="n">
         <v>0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.00114532932639122</v>
+        <v>-0.001145433634519577</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0008109323680400848</v>
+        <v>-0.0008109770715236664</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0006000734865665436</v>
+        <v>-0.0006001591682434082</v>
       </c>
       <c r="JB79" t="n">
         <v>0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.0004564113914966583</v>
+        <v>-0.0004563815891742706</v>
       </c>
       <c r="JB80" t="n">
         <v>0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.0002633519470691681</v>
+        <v>-0.0002633854746818542</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-5.992501974105835e-05</v>
+        <v>-5.987659096717834e-05</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.0002337321639060974</v>
+        <v>0.0002337582409381866</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.0002422593533992767</v>
+        <v>0.0002422630786895752</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0002353750169277191</v>
+        <v>0.0002353228628635406</v>
       </c>
       <c r="JB85" t="n">
         <v>0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0001387596130371094</v>
+        <v>0.0001386366784572601</v>
       </c>
       <c r="JB86" t="n">
         <v>0.2599999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-4.351511597633362e-05</v>
+        <v>-4.363059997558594e-05</v>
       </c>
       <c r="JB87" t="n">
         <v>0.2599999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.0001195706427097321</v>
+        <v>0.0001195147633552551</v>
       </c>
       <c r="JB88" t="n">
         <v>0.2599999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.0002846680581569672</v>
+        <v>0.0002846047282218933</v>
       </c>
       <c r="JB89" t="n">
         <v>0.2599999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.0007876977324485779</v>
+        <v>0.000787641853094101</v>
       </c>
       <c r="JB90" t="n">
         <v>0.2599999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.0004193410277366638</v>
+        <v>0.0004192963242530823</v>
       </c>
       <c r="JB91" t="n">
         <v>0.2599999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>4.898384213447571e-05</v>
+        <v>4.896894097328186e-05</v>
       </c>
       <c r="JB92" t="n">
         <v>0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>3.974884748458862e-06</v>
+        <v>3.963708877563477e-06</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.02000000000000007</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0002566128969192505</v>
+        <v>-0.0002566538751125336</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0004590079188346863</v>
+        <v>-0.0004589557647705078</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.0004889145493507385</v>
+        <v>-0.0004889592528343201</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-5.23589551448822e-05</v>
+        <v>-5.242601037025452e-05</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.02000000000000007</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>4.484131932258606e-05</v>
+        <v>4.48077917098999e-05</v>
       </c>
       <c r="JB98" t="n">
         <v>0.1199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>9.278953075408936e-05</v>
+        <v>9.271129965782166e-05</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0001055151224136353</v>
+        <v>0.0001054294407367706</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.0003549493849277496</v>
+        <v>0.0003549270331859589</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0002830438315868378</v>
+        <v>0.0002830177545547485</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.0004011094570159912</v>
+        <v>0.0004010945558547974</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0005967728793621063</v>
+        <v>0.0005967989563941956</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0006173774600028992</v>
+        <v>0.0006173849105834961</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0006843730807304382</v>
+        <v>0.0006843358278274536</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0007216557860374451</v>
+        <v>0.0007215850055217743</v>
       </c>
       <c r="JB107" t="n">
         <v>0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.0006864182651042938</v>
+        <v>0.0006862729787826538</v>
       </c>
       <c r="JB108" t="n">
         <v>0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0006997138261795044</v>
+        <v>0.0006996393203735352</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0008142478764057159</v>
+        <v>0.0008141063153743744</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.0008651763200759888</v>
+        <v>0.0008648186922073364</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.001108840107917786</v>
+        <v>0.001108646392822266</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.001134958118200302</v>
+        <v>0.001134864985942841</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.001258499920368195</v>
+        <v>0.001258451491594315</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.001240365207195282</v>
+        <v>0.001240290701389313</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.001315202564001083</v>
+        <v>0.001315146684646606</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.002143748104572296</v>
+        <v>0.002143684774637222</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.00234491378068924</v>
+        <v>0.002344828099012375</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3999999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.003407243639230728</v>
+        <v>0.0034070685505867</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3999999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.00258912518620491</v>
+        <v>0.002589013427495956</v>
       </c>
       <c r="JB120" t="n">
         <v>0.2599999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.002218306064605713</v>
+        <v>0.002218212932348251</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.001117009669542313</v>
+        <v>0.001116916537284851</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0002865791320800781</v>
+        <v>0.0002864859998226166</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0001016296446323395</v>
+        <v>0.0001015886664390564</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.0001052431762218475</v>
+        <v>-0.0001052729785442352</v>
       </c>
       <c r="JB125" t="n">
         <v>-1</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.0005270279943943024</v>
+        <v>0.0005270056426525116</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.14</v>
